--- a/2026_10/2026_10_02/HangLung_Amoy_Plaza_and_Fashion_Walk_LMS/clickid.xlsx
+++ b/2026_10/2026_10_02/HangLung_Amoy_Plaza_and_Fashion_Walk_LMS/clickid.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_10\2026_10_02\HangLung_Amoy_Plaza_and_Fashion_Walk_LMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DB33D9-598B-42BB-BF8A-E59A6DC82470}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B426A78-942C-464D-B8F8-EECB75DDF233}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25380" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
